--- a/data/trans_orig/P6715-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P6715-Clase-trans_orig.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W46"/>
+  <dimension ref="A1:W40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si tienen sentido sus tareas del trabajo en 2012</t>
+          <t>Población según si tienen sentido sus tareas del trabajo en 2012 (tasa de respuesta: 99,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -736,7 +736,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4863</t>
+          <t>4988</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,62 +766,62 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>897</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2107</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>5433</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>897</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4516</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>928</t>
+          <t>926</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9238</t>
+          <t>8564</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4998</t>
+          <t>4400</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1824</t>
+          <t>1825</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10101</t>
+          <t>10238</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14894</t>
+          <t>14196</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>34565</t>
+          <t>33515</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2039</t>
+          <t>2083</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12391</t>
+          <t>12889</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>20252</t>
+          <t>20218</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>41171</t>
+          <t>40977</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,24%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31756</t>
+          <t>31092</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>56906</t>
+          <t>54621</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29039</t>
+          <t>29137</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>54023</t>
+          <t>53136</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>65770</t>
+          <t>66449</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>100940</t>
+          <t>101976</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,51%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>217531</t>
+          <t>218236</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>246266</t>
+          <t>247207</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,84%</t>
+          <t>72,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>131775</t>
+          <t>133469</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>158730</t>
+          <t>158815</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>68,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>361095</t>
+          <t>359519</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>400832</t>
+          <t>399605</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>80,37%</t>
         </is>
       </c>
     </row>
@@ -1413,97 +1413,97 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>986</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2130</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4979</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>3,03%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>986</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>5071</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>4939</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>3,09%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>986</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>4985</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>914</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8050</t>
+          <t>7739</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2085</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>925</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7745</t>
+          <t>8761</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11316</t>
+          <t>10661</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26882</t>
+          <t>26561</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17659</t>
+          <t>17653</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>38281</t>
+          <t>39235</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>32858</t>
+          <t>31935</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>60483</t>
+          <t>58993</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>13,99%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>53373</t>
+          <t>53028</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>83958</t>
+          <t>83126</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29082</t>
+          <t>28789</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>52494</t>
+          <t>52629</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>88248</t>
+          <t>87184</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>128425</t>
+          <t>127625</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>30,27%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>152258</t>
+          <t>154030</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>185516</t>
+          <t>187152</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,12%</t>
+          <t>59,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>72,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>83197</t>
+          <t>82812</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>110979</t>
+          <t>109239</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>50,69%</t>
+          <t>50,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,61%</t>
+          <t>66,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>243849</t>
+          <t>243638</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>288617</t>
+          <t>287233</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>57,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,45%</t>
+          <t>68,12%</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5094</t>
+          <t>5657</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,62 +2130,62 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>1022</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>1999</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>6781</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>1,81%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1022</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>5110</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14073</t>
+          <t>11932</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1080</t>
+          <t>1062</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9799</t>
+          <t>9775</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3009</t>
+          <t>3069</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>16561</t>
+          <t>16172</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18377</t>
+          <t>18535</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>39150</t>
+          <t>37829</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12265</t>
+          <t>12287</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>27899</t>
+          <t>29179</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>34626</t>
+          <t>34663</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>59853</t>
+          <t>60270</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,41%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>52637</t>
+          <t>51737</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>79776</t>
+          <t>81839</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9175</t>
+          <t>9207</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24359</t>
+          <t>24173</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>65996</t>
+          <t>65260</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>97237</t>
+          <t>97982</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>25,05%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>166650</t>
+          <t>167401</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>198387</t>
+          <t>200533</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>59,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>71,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>60759</t>
+          <t>60430</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>80294</t>
+          <t>81761</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>54,97%</t>
+          <t>54,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>73,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>235923</t>
+          <t>235454</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>273181</t>
+          <t>274107</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>60,32%</t>
+          <t>60,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>70,08%</t>
         </is>
       </c>
     </row>
@@ -2782,7 +2782,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8101</t>
+          <t>7946</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>934</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8937</t>
+          <t>8819</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,7 +2832,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1951</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11205</t>
+          <t>11249</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3879</t>
+          <t>3763</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>15828</t>
+          <t>15519</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2170</t>
+          <t>2195</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>12923</t>
+          <t>13049</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7937</t>
+          <t>8002</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>23339</t>
+          <t>23446</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>49568</t>
+          <t>51474</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>80044</t>
+          <t>81398</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>41798</t>
+          <t>44224</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>70604</t>
+          <t>71630</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>103308</t>
+          <t>101483</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>144616</t>
+          <t>143156</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,7%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>80352</t>
+          <t>78927</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>116564</t>
+          <t>115023</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>62925</t>
+          <t>62174</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>93188</t>
+          <t>93164</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>151590</t>
+          <t>149158</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>196964</t>
+          <t>196376</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>27,02%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>233200</t>
+          <t>232771</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>275507</t>
+          <t>274647</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>64,54%</t>
+          <t>64,34%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>140428</t>
+          <t>138605</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>174639</t>
+          <t>173178</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>46,23%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>57,76%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>383510</t>
+          <t>386042</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>439282</t>
+          <t>439790</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>53,12%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>60,45%</t>
+          <t>60,52%</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3464,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7268</t>
+          <t>7357</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7390</t>
+          <t>7630</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1054</t>
+          <t>1081</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>10544</t>
+          <t>10565</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1375</t>
+          <t>955</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>10904</t>
+          <t>10155</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>4764</t>
+          <t>4663</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>17762</t>
+          <t>17142</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>7198</t>
+          <t>7994</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>22456</t>
+          <t>23548</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,19%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>22383</t>
+          <t>22536</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>42197</t>
+          <t>43739</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>22838</t>
+          <t>21796</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>45782</t>
+          <t>43655</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>50342</t>
+          <t>51308</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>79403</t>
+          <t>80474</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,57%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>31050</t>
+          <t>30386</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>52491</t>
+          <t>54109</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>31637</t>
+          <t>32473</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>56327</t>
+          <t>56384</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>67218</t>
+          <t>68657</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>100952</t>
+          <t>102532</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>31,3%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>62145</t>
+          <t>60763</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>84406</t>
+          <t>85787</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>55,55%</t>
+          <t>56,46%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>74187</t>
+          <t>73382</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>102501</t>
+          <t>101734</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>57,92%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>142618</t>
+          <t>141651</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>181358</t>
+          <t>179259</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>43,24%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>55,37%</t>
+          <t>54,72%</t>
         </is>
       </c>
     </row>
@@ -4121,7 +4121,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -4131,107 +4131,107 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6250</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2089</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12875</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6176</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2871</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12849</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12425</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6761</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>20739</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -4244,107 +4244,107 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21970</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>13969</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>34146</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21279</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>13717</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>32411</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>41</t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>43249</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>30440</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>57400</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -4357,107 +4357,107 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>155</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>163687</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>140832</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>187550</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>131</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>141189</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>119466</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>165605</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>286</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>304876</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>270698</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>338308</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>14,31%</t>
         </is>
       </c>
     </row>
@@ -4470,107 +4470,107 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>299</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>313553</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>282577</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>346216</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>203</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>215608</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>190680</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>245139</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>502</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>529161</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>490877</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>568812</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,06%</t>
         </is>
       </c>
     </row>
@@ -4583,107 +4583,107 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>852</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>914292</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>878206</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>949987</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>64,4%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>61,86%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>66,91%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>513</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>560283</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>524803</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>591828</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,56%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>62,66%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1365</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1474576</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1428185</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1523844</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>62,37%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>64,45%</t>
         </is>
       </c>
     </row>
@@ -4696,804 +4696,121 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1333</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1419752</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1419752</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1419752</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>873</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>944535</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>944535</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>944535</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2206</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2364287</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2364287</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2364287</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>Nunca</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>6250</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>2060</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>13477</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>6176</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>2157</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>13403</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>12425</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>6993</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t>21148</t>
-        </is>
-      </c>
-      <c r="U40" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="W40" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="n"/>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>Solo alguna vez</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>21970</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>14569</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>33731</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>2,38%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>21279</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>13620</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>32131</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>2,25%</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>3,4%</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>43249</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>31570</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t>58511</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="V41" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
-      <c r="W41" s="2" t="inlineStr">
-        <is>
-          <t>2,47%</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="n"/>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>Algunas veces</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>163687</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>140828</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>190083</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>11,53%</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>9,92%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>13,39%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>141189</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>120821</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>165256</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>14,95%</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>12,79%</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>17,5%</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t>286</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t>304876</t>
-        </is>
-      </c>
-      <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t>271669</t>
-        </is>
-      </c>
-      <c r="T42" s="2" t="inlineStr">
-        <is>
-          <t>336278</t>
-        </is>
-      </c>
-      <c r="U42" s="2" t="inlineStr">
-        <is>
-          <t>12,9%</t>
-        </is>
-      </c>
-      <c r="V42" s="2" t="inlineStr">
-        <is>
-          <t>11,49%</t>
-        </is>
-      </c>
-      <c r="W42" s="2" t="inlineStr">
-        <is>
-          <t>14,22%</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="n"/>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>Muchas veces</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>299</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>313553</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>280558</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>346860</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>22,09%</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>19,76%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>24,43%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>215608</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>188506</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>242265</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>22,83%</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t>19,96%</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>25,65%</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t>502</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>529161</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t>483928</t>
-        </is>
-      </c>
-      <c r="T43" s="2" t="inlineStr">
-        <is>
-          <t>565719</t>
-        </is>
-      </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t>22,38%</t>
-        </is>
-      </c>
-      <c r="V43" s="2" t="inlineStr">
-        <is>
-          <t>20,47%</t>
-        </is>
-      </c>
-      <c r="W43" s="2" t="inlineStr">
-        <is>
-          <t>23,93%</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="n"/>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>Siempre</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>852</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>914292</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>877969</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>951783</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>64,4%</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>61,84%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>67,04%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>513</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>560283</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>528804</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>592315</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>59,32%</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>55,99%</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>62,71%</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t>1365</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t>1474576</t>
-        </is>
-      </c>
-      <c r="S44" s="2" t="inlineStr">
-        <is>
-          <t>1429012</t>
-        </is>
-      </c>
-      <c r="T44" s="2" t="inlineStr">
-        <is>
-          <t>1531251</t>
-        </is>
-      </c>
-      <c r="U44" s="2" t="inlineStr">
-        <is>
-          <t>62,37%</t>
-        </is>
-      </c>
-      <c r="V44" s="2" t="inlineStr">
-        <is>
-          <t>60,44%</t>
-        </is>
-      </c>
-      <c r="W44" s="2" t="inlineStr">
-        <is>
-          <t>64,77%</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="n"/>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>1333</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>1419752</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>1419752</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>1419752</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>873</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>944535</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>944535</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>944535</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q45" s="2" t="inlineStr">
-        <is>
-          <t>2206</t>
-        </is>
-      </c>
-      <c r="R45" s="2" t="inlineStr">
-        <is>
-          <t>2364287</t>
-        </is>
-      </c>
-      <c r="S45" s="2" t="inlineStr">
-        <is>
-          <t>2364287</t>
-        </is>
-      </c>
-      <c r="T45" s="2" t="inlineStr">
-        <is>
-          <t>2364287</t>
-        </is>
-      </c>
-      <c r="U45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A22:A27"/>
-    <mergeCell ref="A40:A45"/>
     <mergeCell ref="A4:A9"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A34:A39"/>
@@ -5513,7 +4830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W46"/>
+  <dimension ref="A1:W40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5544,7 +4861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si tienen sentido sus tareas del trabajo en 2016</t>
+          <t>Población según si tienen sentido sus tareas del trabajo en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5744,7 +5061,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7058</t>
+          <t>6803</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5759,7 +5076,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5779,7 +5096,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7180</t>
+          <t>6039</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5794,7 +5111,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5809,12 +5126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>931</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9232</t>
+          <t>8955</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5829,7 +5146,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5912</t>
+          <t>5975</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21279</t>
+          <t>21445</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5867,12 +5184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5887,12 +5204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>1889</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11629</t>
+          <t>10965</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5902,12 +5219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5922,12 +5239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9545</t>
+          <t>9831</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26492</t>
+          <t>26501</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5937,7 +5254,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -5965,12 +5282,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14367</t>
+          <t>14049</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>33755</t>
+          <t>34839</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5980,12 +5297,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6000,12 +5317,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10170</t>
+          <t>10202</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26055</t>
+          <t>26202</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6015,12 +5332,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6035,12 +5352,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>28897</t>
+          <t>27995</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>54587</t>
+          <t>53802</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6050,12 +5367,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,92%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +5395,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35733</t>
+          <t>35940</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>62180</t>
+          <t>61872</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6093,82 +5410,82 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
+          <t>12,91%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>22,23%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>30864</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>21859</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>43519</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>14,41%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>10,21%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>20,32%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>78813</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>63220</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>96491</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>16,0%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>12,84%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>22,34%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>30864</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>21875</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>42411</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>14,41%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>10,21%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>19,8%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>78813</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>64748</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>97112</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>16,0%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>13,15%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,59%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +5508,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>178433</t>
+          <t>176668</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>210683</t>
+          <t>209378</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6206,12 +5523,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>64,11%</t>
+          <t>63,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,69%</t>
+          <t>75,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6226,12 +5543,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>145726</t>
+          <t>146163</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>171953</t>
+          <t>171280</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6241,12 +5558,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,04%</t>
+          <t>68,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>79,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6261,12 +5578,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>333522</t>
+          <t>332720</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>373833</t>
+          <t>375401</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6276,12 +5593,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>67,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>76,22%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +5738,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>918</t>
+          <t>904</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9066</t>
+          <t>8051</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6436,12 +5753,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6461,7 +5778,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7197</t>
+          <t>9602</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6476,7 +5793,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6491,12 +5808,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1913</t>
+          <t>1907</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10897</t>
+          <t>11089</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6511,7 +5828,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +5851,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1019</t>
+          <t>1049</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8889</t>
+          <t>9002</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6549,12 +5866,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6569,12 +5886,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3820</t>
+          <t>3829</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16384</t>
+          <t>15722</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6589,7 +5906,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6604,12 +5921,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6111</t>
+          <t>5808</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>19794</t>
+          <t>20565</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6619,12 +5936,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +5964,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23268</t>
+          <t>24662</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>48835</t>
+          <t>47499</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6662,12 +5979,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6682,12 +5999,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>21008</t>
+          <t>20280</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>40949</t>
+          <t>40833</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6697,12 +6014,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6717,12 +6034,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>49289</t>
+          <t>49695</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>82732</t>
+          <t>80483</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6732,12 +6049,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,58%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6077,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>56919</t>
+          <t>56689</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>86785</t>
+          <t>86583</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6775,12 +6092,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6795,12 +6112,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>51164</t>
+          <t>51757</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>79323</t>
+          <t>77936</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6810,12 +6127,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6830,12 +6147,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>114171</t>
+          <t>114813</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>157194</t>
+          <t>155335</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6845,12 +6162,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>35,86%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6190,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>115985</t>
+          <t>116123</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>149478</t>
+          <t>146825</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6888,12 +6205,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>47,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>60,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6908,12 +6225,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>70009</t>
+          <t>70974</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>99579</t>
+          <t>99693</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6923,12 +6240,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>52,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6943,12 +6260,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>193262</t>
+          <t>196867</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>238520</t>
+          <t>240913</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6958,12 +6275,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>44,61%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>55,61%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +6420,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3592</t>
+          <t>3602</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16092</t>
+          <t>17297</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7118,12 +6435,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7138,12 +6455,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1920</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7153,12 +6470,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7173,12 +6490,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3838</t>
+          <t>3703</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17863</t>
+          <t>17442</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7188,12 +6505,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,13%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +6533,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7963</t>
+          <t>7548</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24324</t>
+          <t>23917</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7231,12 +6548,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7256,7 +6573,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4799</t>
+          <t>4443</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7271,7 +6588,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7286,12 +6603,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9156</t>
+          <t>8638</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>28002</t>
+          <t>25682</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7301,12 +6618,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,03%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +6646,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13506</t>
+          <t>13666</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>31693</t>
+          <t>31528</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7344,12 +6661,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7364,12 +6681,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1945</t>
+          <t>1883</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10832</t>
+          <t>10636</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7379,12 +6696,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7399,12 +6716,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>17301</t>
+          <t>17019</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>36148</t>
+          <t>37220</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7414,12 +6731,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>13,08%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +6759,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>51450</t>
+          <t>51111</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>78406</t>
+          <t>78710</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7457,12 +6774,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7477,12 +6794,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10223</t>
+          <t>11077</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24463</t>
+          <t>25037</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7492,12 +6809,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7512,12 +6829,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>67701</t>
+          <t>67650</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>99030</t>
+          <t>97568</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7527,12 +6844,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>34,3%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +6872,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>95173</t>
+          <t>93188</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>123786</t>
+          <t>124190</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7570,12 +6887,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>56,98%</t>
+          <t>57,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7590,12 +6907,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>36658</t>
+          <t>36598</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>51884</t>
+          <t>51282</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7605,12 +6922,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>54,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>76,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7625,12 +6942,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>136166</t>
+          <t>136019</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>169709</t>
+          <t>169866</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7640,12 +6957,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>47,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>59,72%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7102,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3311</t>
+          <t>3245</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15220</t>
+          <t>14998</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7800,12 +7117,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7825,7 +7142,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5943</t>
+          <t>6748</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7840,7 +7157,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7855,12 +7172,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4336</t>
+          <t>4458</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>18129</t>
+          <t>17694</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7870,12 +7187,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -7898,12 +7215,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9454</t>
+          <t>9424</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>26019</t>
+          <t>26484</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7918,7 +7235,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7933,12 +7250,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>7753</t>
+          <t>7893</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>22486</t>
+          <t>22759</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7948,12 +7265,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7968,12 +7285,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>20478</t>
+          <t>19095</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>43738</t>
+          <t>41644</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7983,12 +7300,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -8011,12 +7328,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>68171</t>
+          <t>69672</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>102255</t>
+          <t>104227</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8026,12 +7343,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8046,12 +7363,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>53761</t>
+          <t>53462</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>83390</t>
+          <t>83021</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8061,12 +7378,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8081,12 +7398,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>129829</t>
+          <t>129795</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>174233</t>
+          <t>174954</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8101,7 +7418,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,42%</t>
         </is>
       </c>
     </row>
@@ -8124,12 +7441,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>142412</t>
+          <t>143939</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>185138</t>
+          <t>184266</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8139,12 +7456,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8159,12 +7476,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>97030</t>
+          <t>96943</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>131872</t>
+          <t>132113</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8174,12 +7491,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8194,12 +7511,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>251694</t>
+          <t>248529</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>304267</t>
+          <t>305530</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8209,12 +7526,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>35,66%</t>
         </is>
       </c>
     </row>
@@ -8237,12 +7554,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>194649</t>
+          <t>193495</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>240894</t>
+          <t>237232</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8252,12 +7569,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>49,29%</t>
+          <t>48,54%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8272,12 +7589,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>149939</t>
+          <t>151877</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>189482</t>
+          <t>191813</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8287,12 +7604,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>40,74%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>52,12%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8307,12 +7624,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>359075</t>
+          <t>360624</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>417137</t>
+          <t>416607</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8322,12 +7639,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>42,09%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>48,62%</t>
         </is>
       </c>
     </row>
@@ -8467,12 +7784,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>8464</t>
+          <t>8327</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8487,7 +7804,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8502,12 +7819,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5153</t>
+          <t>5104</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>18352</t>
+          <t>17974</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8517,12 +7834,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8537,12 +7854,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>7266</t>
+          <t>8040</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>21212</t>
+          <t>22136</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8552,12 +7869,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -8580,12 +7897,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4087</t>
+          <t>4082</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>16980</t>
+          <t>16333</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8595,12 +7912,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8615,12 +7932,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3904</t>
+          <t>3829</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>15188</t>
+          <t>15013</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8630,12 +7947,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8650,12 +7967,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>9833</t>
+          <t>9572</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>25582</t>
+          <t>25856</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8665,12 +7982,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,6%</t>
         </is>
       </c>
     </row>
@@ -8693,12 +8010,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>38734</t>
+          <t>38282</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>63882</t>
+          <t>63425</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8708,12 +8025,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8728,12 +8045,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>29858</t>
+          <t>31217</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>53155</t>
+          <t>54250</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8743,12 +8060,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8763,12 +8080,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>74001</t>
+          <t>75542</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>110022</t>
+          <t>110191</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8778,12 +8095,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,14%</t>
         </is>
       </c>
     </row>
@@ -8806,12 +8123,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>44367</t>
+          <t>42325</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>70262</t>
+          <t>68837</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8821,12 +8138,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8841,12 +8158,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>49487</t>
+          <t>49517</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>75859</t>
+          <t>75952</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8856,12 +8173,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8876,12 +8193,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>101150</t>
+          <t>99509</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>137284</t>
+          <t>137222</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8891,12 +8208,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>35,04%</t>
         </is>
       </c>
     </row>
@@ -8919,12 +8236,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>62287</t>
+          <t>62249</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>90070</t>
+          <t>90856</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8934,12 +8251,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8954,12 +8271,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>63444</t>
+          <t>63440</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>90827</t>
+          <t>90014</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8974,7 +8291,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8989,12 +8306,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>133894</t>
+          <t>133272</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>170306</t>
+          <t>170440</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9004,12 +8321,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>43,53%</t>
         </is>
       </c>
     </row>
@@ -9129,7 +8446,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -9139,107 +8456,107 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>23429</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14382</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>35524</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>16260</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9244</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>25338</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>37</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>39689</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>28181</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>55123</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -9252,107 +8569,107 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>49</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>54773</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>41488</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>71835</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>36082</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>25844</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>48079</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>85</t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>90854</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>74592</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>112163</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -9365,107 +8682,107 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>192</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>214240</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>185269</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>243199</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>156</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>159550</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>138216</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>185525</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>348</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>373791</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>333823</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>411101</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,72%</t>
         </is>
       </c>
     </row>
@@ -9478,107 +8795,107 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>381</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>402449</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>370270</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>438466</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>287</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>288412</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>264545</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>325193</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>668</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>690861</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>643675</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>739015</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>30,06%</t>
         </is>
       </c>
     </row>
@@ -9591,107 +8908,107 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>680</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>727431</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>687163</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>763921</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,14%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>53,71%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>517</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>535915</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>499382</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>563377</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,72%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>54,37%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1197</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1263346</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1213419</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1315291</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>51,39%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>49,36%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>53,5%</t>
         </is>
       </c>
     </row>
@@ -9704,804 +9021,121 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1323</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1422322</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1422322</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1422322</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1036219</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1036219</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1036219</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2335</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2458541</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2458541</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2458541</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>Nunca</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>23429</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>14845</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>34941</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>16260</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>9251</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>25462</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>39689</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>28415</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t>53089</t>
-        </is>
-      </c>
-      <c r="U40" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-      <c r="W40" s="2" t="inlineStr">
-        <is>
-          <t>2,16%</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="n"/>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>Solo alguna vez</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>54773</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>40101</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>71694</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>3,85%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>2,82%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>5,04%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>36082</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>26561</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>51574</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>3,48%</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>2,56%</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>4,98%</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>90854</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>72535</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t>116507</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t>3,7%</t>
-        </is>
-      </c>
-      <c r="V41" s="2" t="inlineStr">
-        <is>
-          <t>2,95%</t>
-        </is>
-      </c>
-      <c r="W41" s="2" t="inlineStr">
-        <is>
-          <t>4,74%</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="n"/>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>Algunas veces</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>214240</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>187394</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>245956</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t>15,06%</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>13,18%</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>17,29%</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>159550</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
-        <is>
-          <t>137111</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>183714</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>15,4%</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="inlineStr">
-        <is>
-          <t>13,23%</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>17,73%</t>
-        </is>
-      </c>
-      <c r="Q42" s="2" t="inlineStr">
-        <is>
-          <t>348</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr">
-        <is>
-          <t>373791</t>
-        </is>
-      </c>
-      <c r="S42" s="2" t="inlineStr">
-        <is>
-          <t>337594</t>
-        </is>
-      </c>
-      <c r="T42" s="2" t="inlineStr">
-        <is>
-          <t>409905</t>
-        </is>
-      </c>
-      <c r="U42" s="2" t="inlineStr">
-        <is>
-          <t>15,2%</t>
-        </is>
-      </c>
-      <c r="V42" s="2" t="inlineStr">
-        <is>
-          <t>13,73%</t>
-        </is>
-      </c>
-      <c r="W42" s="2" t="inlineStr">
-        <is>
-          <t>16,67%</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="n"/>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>Muchas veces</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>381</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>402449</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>365035</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>439389</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>28,3%</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>25,66%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>30,89%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>287</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>288412</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>259713</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>315531</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>27,83%</t>
-        </is>
-      </c>
-      <c r="O43" s="2" t="inlineStr">
-        <is>
-          <t>25,06%</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="inlineStr">
-        <is>
-          <t>30,45%</t>
-        </is>
-      </c>
-      <c r="Q43" s="2" t="inlineStr">
-        <is>
-          <t>668</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>690861</t>
-        </is>
-      </c>
-      <c r="S43" s="2" t="inlineStr">
-        <is>
-          <t>642246</t>
-        </is>
-      </c>
-      <c r="T43" s="2" t="inlineStr">
-        <is>
-          <t>733535</t>
-        </is>
-      </c>
-      <c r="U43" s="2" t="inlineStr">
-        <is>
-          <t>28,1%</t>
-        </is>
-      </c>
-      <c r="V43" s="2" t="inlineStr">
-        <is>
-          <t>26,12%</t>
-        </is>
-      </c>
-      <c r="W43" s="2" t="inlineStr">
-        <is>
-          <t>29,84%</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="n"/>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>Siempre</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>680</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>727431</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>689035</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>765355</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>51,14%</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>48,44%</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>53,81%</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>517</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>535915</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>506871</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>567140</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>51,72%</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>48,92%</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>54,73%</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t>1197</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="inlineStr">
-        <is>
-          <t>1263346</t>
-        </is>
-      </c>
-      <c r="S44" s="2" t="inlineStr">
-        <is>
-          <t>1214696</t>
-        </is>
-      </c>
-      <c r="T44" s="2" t="inlineStr">
-        <is>
-          <t>1310605</t>
-        </is>
-      </c>
-      <c r="U44" s="2" t="inlineStr">
-        <is>
-          <t>51,39%</t>
-        </is>
-      </c>
-      <c r="V44" s="2" t="inlineStr">
-        <is>
-          <t>49,41%</t>
-        </is>
-      </c>
-      <c r="W44" s="2" t="inlineStr">
-        <is>
-          <t>53,31%</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="n"/>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>1323</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>1422322</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>1422322</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>1422322</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>1012</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>1036219</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>1036219</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>1036219</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="Q45" s="2" t="inlineStr">
-        <is>
-          <t>2335</t>
-        </is>
-      </c>
-      <c r="R45" s="2" t="inlineStr">
-        <is>
-          <t>2458541</t>
-        </is>
-      </c>
-      <c r="S45" s="2" t="inlineStr">
-        <is>
-          <t>2458541</t>
-        </is>
-      </c>
-      <c r="T45" s="2" t="inlineStr">
-        <is>
-          <t>2458541</t>
-        </is>
-      </c>
-      <c r="U45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="V45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="W45" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="J1:P1"/>
     <mergeCell ref="A22:A27"/>
-    <mergeCell ref="A40:A45"/>
     <mergeCell ref="A4:A9"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A34:A39"/>

--- a/data/trans_orig/P6715-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P6715-Clase-trans_orig.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4988</t>
+          <t>4467</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5433</t>
+          <t>4496</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>924</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8564</t>
+          <t>8644</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4400</t>
+          <t>4931</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1825</t>
+          <t>1832</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10238</t>
+          <t>10295</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14196</t>
+          <t>14367</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>33515</t>
+          <t>33686</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2083</t>
+          <t>2134</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12889</t>
+          <t>13029</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>20218</t>
+          <t>19544</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>40977</t>
+          <t>40745</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,19%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31092</t>
+          <t>32048</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>54621</t>
+          <t>54878</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29137</t>
+          <t>28582</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>53136</t>
+          <t>52969</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>66449</t>
+          <t>66773</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>101976</t>
+          <t>102410</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,6%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>218236</t>
+          <t>218025</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>247207</t>
+          <t>246886</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,07%</t>
+          <t>72,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>133469</t>
+          <t>133940</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>158815</t>
+          <t>159738</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>68,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>82,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>359519</t>
+          <t>359750</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>399605</t>
+          <t>399729</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>72,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>80,39%</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>5890</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4939</t>
+          <t>5962</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>931</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7739</t>
+          <t>9353</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>923</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8761</t>
+          <t>8252</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10661</t>
+          <t>10846</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26561</t>
+          <t>27535</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17653</t>
+          <t>17649</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>39235</t>
+          <t>37396</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>31935</t>
+          <t>32810</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>58993</t>
+          <t>58170</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,8%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>53028</t>
+          <t>53816</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>83126</t>
+          <t>84970</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28789</t>
+          <t>29333</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>52629</t>
+          <t>51584</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>87184</t>
+          <t>88905</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>127625</t>
+          <t>126061</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>29,9%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>154030</t>
+          <t>152806</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>187152</t>
+          <t>185794</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,67%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>82812</t>
+          <t>82350</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>109239</t>
+          <t>109015</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>50,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>66,55%</t>
+          <t>66,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>243638</t>
+          <t>245270</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>287233</t>
+          <t>286127</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>58,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,12%</t>
+          <t>67,86%</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5657</t>
+          <t>5106</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6781</t>
+          <t>4132</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -2213,7 +2213,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11932</t>
+          <t>11532</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1062</t>
+          <t>1163</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9775</t>
+          <t>9820</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3069</t>
+          <t>3048</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>16172</t>
+          <t>17404</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>18535</t>
+          <t>18308</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>37829</t>
+          <t>37168</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12287</t>
+          <t>12149</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>29179</t>
+          <t>28908</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>34663</t>
+          <t>35074</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>60270</t>
+          <t>60247</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,4%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>51737</t>
+          <t>52648</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>81839</t>
+          <t>81617</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9207</t>
+          <t>9503</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24173</t>
+          <t>24420</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>65260</t>
+          <t>66220</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>97982</t>
+          <t>97447</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>24,92%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>167401</t>
+          <t>166514</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>200533</t>
+          <t>199197</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>59,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>70,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>60430</t>
+          <t>60589</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>81761</t>
+          <t>80851</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>54,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>73,98%</t>
+          <t>73,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>235454</t>
+          <t>236766</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>274107</t>
+          <t>272856</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>60,2%</t>
+          <t>60,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>70,08%</t>
+          <t>69,76%</t>
         </is>
       </c>
     </row>
@@ -2782,7 +2782,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7946</t>
+          <t>8093</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>934</t>
+          <t>935</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8819</t>
+          <t>10231</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2832,7 +2832,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>1977</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11249</t>
+          <t>12679</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3763</t>
+          <t>3881</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>15519</t>
+          <t>15085</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>2325</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>13049</t>
+          <t>13216</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>8002</t>
+          <t>8239</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>23446</t>
+          <t>23815</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>51474</t>
+          <t>50719</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>81398</t>
+          <t>81236</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>44224</t>
+          <t>44034</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>71630</t>
+          <t>70494</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>101483</t>
+          <t>101381</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>143156</t>
+          <t>146844</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>20,21%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>78927</t>
+          <t>80102</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>115023</t>
+          <t>115757</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>62174</t>
+          <t>61986</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>93164</t>
+          <t>91854</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>149158</t>
+          <t>148343</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>196376</t>
+          <t>196461</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>27,03%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>232771</t>
+          <t>233873</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>274647</t>
+          <t>275328</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>54,78%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>64,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>138605</t>
+          <t>141417</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>173178</t>
+          <t>175328</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>57,76%</t>
+          <t>58,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>386042</t>
+          <t>384738</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>439790</t>
+          <t>442527</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>60,52%</t>
+          <t>60,89%</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3464,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7357</t>
+          <t>6405</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7630</t>
+          <t>7467</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1081</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>10565</t>
+          <t>10641</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>10155</t>
+          <t>10450</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>17142</t>
+          <t>17745</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>7994</t>
+          <t>7904</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>23548</t>
+          <t>22663</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>6,92%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>22536</t>
+          <t>22040</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>43739</t>
+          <t>43709</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>21796</t>
+          <t>23973</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>43655</t>
+          <t>45133</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>51308</t>
+          <t>51605</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>80474</t>
+          <t>80676</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,63%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>30386</t>
+          <t>30599</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>54109</t>
+          <t>52521</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>32473</t>
+          <t>33206</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>56384</t>
+          <t>57036</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>68657</t>
+          <t>69241</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>102532</t>
+          <t>100908</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>30,81%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>60763</t>
+          <t>61380</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>85787</t>
+          <t>85590</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>56,46%</t>
+          <t>56,33%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>73382</t>
+          <t>73427</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>101734</t>
+          <t>101281</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>41,81%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>57,92%</t>
+          <t>57,67%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>141651</t>
+          <t>142378</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>179259</t>
+          <t>178959</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>54,63%</t>
         </is>
       </c>
     </row>
@@ -4141,12 +4141,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2089</t>
+          <t>2091</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>12875</t>
+          <t>12716</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4161,77 +4161,77 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>6176</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>2137</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>13422</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr">
+        <is>
+          <t>12425</t>
+        </is>
+      </c>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>7044</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>21531</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
           <t>0,91%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>6176</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>2871</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>12849</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>12425</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>6761</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>20739</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="W34" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -4254,12 +4254,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>13969</t>
+          <t>14133</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>34146</t>
+          <t>33757</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4289,12 +4289,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>13717</t>
+          <t>13484</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>32411</t>
+          <t>32308</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4324,12 +4324,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>30440</t>
+          <t>31557</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>57400</t>
+          <t>58657</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -4367,12 +4367,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>140832</t>
+          <t>140876</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>187550</t>
+          <t>189782</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4402,12 +4402,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>119466</t>
+          <t>118568</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>165605</t>
+          <t>165440</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4437,12 +4437,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>270698</t>
+          <t>271083</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>338308</t>
+          <t>337885</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,29%</t>
         </is>
       </c>
     </row>
@@ -4480,12 +4480,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>282577</t>
+          <t>282984</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>346216</t>
+          <t>347676</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4495,12 +4495,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>190680</t>
+          <t>188304</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>245139</t>
+          <t>245949</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4530,12 +4530,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>490877</t>
+          <t>487004</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>568812</t>
+          <t>571375</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,17%</t>
         </is>
       </c>
     </row>
@@ -4593,12 +4593,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>878206</t>
+          <t>878454</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>949987</t>
+          <t>951657</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>61,87%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>66,91%</t>
+          <t>67,03%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>524803</t>
+          <t>528088</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>591828</t>
+          <t>591976</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>55,56%</t>
+          <t>55,91%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>62,66%</t>
+          <t>62,67%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1428185</t>
+          <t>1424726</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1523844</t>
+          <t>1524689</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>60,41%</t>
+          <t>60,26%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>64,49%</t>
         </is>
       </c>
     </row>
@@ -5061,7 +5061,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6803</t>
+          <t>7789</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6039</t>
+          <t>6772</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>931</t>
+          <t>941</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8955</t>
+          <t>9243</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5975</t>
+          <t>5843</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21445</t>
+          <t>20354</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1889</t>
+          <t>1854</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10965</t>
+          <t>10633</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9831</t>
+          <t>9616</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26501</t>
+          <t>27146</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14049</t>
+          <t>14783</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>34839</t>
+          <t>35823</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10202</t>
+          <t>10501</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26202</t>
+          <t>27004</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>27995</t>
+          <t>27168</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>53802</t>
+          <t>55026</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,17%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35940</t>
+          <t>36624</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>61872</t>
+          <t>62244</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21859</t>
+          <t>21553</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43519</t>
+          <t>43784</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>63220</t>
+          <t>62951</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>96491</t>
+          <t>97236</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,74%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>176668</t>
+          <t>176212</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>209378</t>
+          <t>208874</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,47%</t>
+          <t>63,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>146163</t>
+          <t>146515</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>171280</t>
+          <t>172562</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,25%</t>
+          <t>68,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>80,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>332720</t>
+          <t>331660</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>375401</t>
+          <t>374350</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>67,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>76,01%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>904</t>
+          <t>915</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8051</t>
+          <t>8811</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5778,7 +5778,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9602</t>
+          <t>7960</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>1938</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11089</t>
+          <t>11126</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1049</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9002</t>
+          <t>8728</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3829</t>
+          <t>3863</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15722</t>
+          <t>15865</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5808</t>
+          <t>5827</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>20565</t>
+          <t>19481</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24662</t>
+          <t>23083</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>47499</t>
+          <t>46531</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>20280</t>
+          <t>21353</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>40833</t>
+          <t>40374</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>49695</t>
+          <t>50086</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>80483</t>
+          <t>80145</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,5%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>56689</t>
+          <t>55946</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>86583</t>
+          <t>85289</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>51757</t>
+          <t>52085</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>77936</t>
+          <t>77416</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>114813</t>
+          <t>115804</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>155335</t>
+          <t>154112</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>35,57%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>116123</t>
+          <t>116794</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>146825</t>
+          <t>147009</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>47,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>60,17%</t>
+          <t>60,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>70974</t>
+          <t>71563</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>99693</t>
+          <t>99587</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>52,7%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>196867</t>
+          <t>194870</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>240913</t>
+          <t>239631</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>44,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>55,61%</t>
+          <t>55,32%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3602</t>
+          <t>3608</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17297</t>
+          <t>16511</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6440,7 +6440,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3703</t>
+          <t>3674</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17442</t>
+          <t>16730</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>5,88%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7548</t>
+          <t>7752</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23917</t>
+          <t>24279</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4443</t>
+          <t>3684</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8638</t>
+          <t>8914</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>25682</t>
+          <t>25245</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,87%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13666</t>
+          <t>13456</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>31528</t>
+          <t>31310</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1883</t>
+          <t>1814</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10636</t>
+          <t>10658</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>17019</t>
+          <t>17443</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>37220</t>
+          <t>37148</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,06%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>51111</t>
+          <t>50032</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>78710</t>
+          <t>77664</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11077</t>
+          <t>10387</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25037</t>
+          <t>24993</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>37,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>67650</t>
+          <t>67044</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>97568</t>
+          <t>97202</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,17%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>93188</t>
+          <t>94093</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>124190</t>
+          <t>124479</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>57,16%</t>
+          <t>57,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>36598</t>
+          <t>35556</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>51282</t>
+          <t>50723</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>54,46%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>75,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>136019</t>
+          <t>135646</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>169866</t>
+          <t>170789</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>59,72%</t>
+          <t>60,04%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3245</t>
+          <t>3073</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14998</t>
+          <t>14561</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7142,7 +7142,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6748</t>
+          <t>6905</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7157,7 +7157,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4458</t>
+          <t>4301</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>17694</t>
+          <t>17553</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9424</t>
+          <t>9028</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>26484</t>
+          <t>25649</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>7893</t>
+          <t>7589</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>22759</t>
+          <t>23204</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>19095</t>
+          <t>20731</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>41644</t>
+          <t>41609</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>69672</t>
+          <t>68381</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>104227</t>
+          <t>102185</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>53462</t>
+          <t>55084</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>83021</t>
+          <t>84914</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>129795</t>
+          <t>130430</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>174954</t>
+          <t>175143</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,44%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>143939</t>
+          <t>141166</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>184266</t>
+          <t>185502</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>96943</t>
+          <t>97238</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>132113</t>
+          <t>132031</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>35,87%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>248529</t>
+          <t>248945</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>305530</t>
+          <t>304247</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,51%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>193495</t>
+          <t>194659</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>237232</t>
+          <t>237069</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>39,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>48,54%</t>
+          <t>48,51%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>151877</t>
+          <t>152142</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>191813</t>
+          <t>190347</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>52,12%</t>
+          <t>51,72%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>360624</t>
+          <t>358720</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>416607</t>
+          <t>420281</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>49,05%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>8327</t>
+          <t>8589</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7804,7 +7804,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>5104</t>
+          <t>5034</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>17974</t>
+          <t>17888</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>8040</t>
+          <t>7284</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>22136</t>
+          <t>21932</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -7897,12 +7897,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4082</t>
+          <t>3981</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>16333</t>
+          <t>16140</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7912,12 +7912,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7932,12 +7932,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3829</t>
+          <t>3647</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>15013</t>
+          <t>14816</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7947,12 +7947,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7967,12 +7967,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>9572</t>
+          <t>10139</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>25856</t>
+          <t>26457</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7982,12 +7982,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,76%</t>
         </is>
       </c>
     </row>
@@ -8010,12 +8010,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>38282</t>
+          <t>39295</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>63425</t>
+          <t>65647</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8025,12 +8025,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8045,12 +8045,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>31217</t>
+          <t>30161</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>54250</t>
+          <t>53121</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>75542</t>
+          <t>74718</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>110191</t>
+          <t>109471</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>27,96%</t>
         </is>
       </c>
     </row>
@@ -8123,12 +8123,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>42325</t>
+          <t>43899</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>68837</t>
+          <t>68617</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8138,12 +8138,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8158,12 +8158,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>49517</t>
+          <t>50201</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>75952</t>
+          <t>75899</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>99509</t>
+          <t>101959</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>137222</t>
+          <t>137908</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>35,04%</t>
+          <t>35,22%</t>
         </is>
       </c>
     </row>
@@ -8236,12 +8236,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>62249</t>
+          <t>61642</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>90856</t>
+          <t>89577</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8251,12 +8251,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>46,18%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8271,12 +8271,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>63440</t>
+          <t>62748</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>90014</t>
+          <t>90240</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>45,66%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8306,12 +8306,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>133272</t>
+          <t>134123</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>170440</t>
+          <t>171499</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>43,8%</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>14382</t>
+          <t>15462</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>35524</t>
+          <t>35474</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8481,12 +8481,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8501,12 +8501,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>9244</t>
+          <t>9273</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>25338</t>
+          <t>26368</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>28181</t>
+          <t>27980</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>55123</t>
+          <t>53716</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -8579,12 +8579,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>41488</t>
+          <t>41094</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>71835</t>
+          <t>70599</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8594,12 +8594,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8614,12 +8614,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>25844</t>
+          <t>25138</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>48079</t>
+          <t>48535</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8649,12 +8649,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>74592</t>
+          <t>72710</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>112163</t>
+          <t>112471</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -8692,12 +8692,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>185269</t>
+          <t>186250</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>243199</t>
+          <t>244042</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8707,12 +8707,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8727,12 +8727,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>138216</t>
+          <t>136327</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>185525</t>
+          <t>182368</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8762,12 +8762,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>333823</t>
+          <t>336898</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>411101</t>
+          <t>415843</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,91%</t>
         </is>
       </c>
     </row>
@@ -8805,12 +8805,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>370270</t>
+          <t>367716</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>438466</t>
+          <t>436226</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8820,12 +8820,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>264545</t>
+          <t>261132</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>325193</t>
+          <t>317851</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8875,12 +8875,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>643675</t>
+          <t>639398</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>739015</t>
+          <t>733021</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>29,82%</t>
         </is>
       </c>
     </row>
@@ -8918,12 +8918,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>687163</t>
+          <t>690276</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>763921</t>
+          <t>766886</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8933,12 +8933,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>48,53%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>53,92%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8953,12 +8953,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>499382</t>
+          <t>502441</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>563377</t>
+          <t>566846</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>48,49%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>54,7%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -8988,12 +8988,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1213419</t>
+          <t>1208027</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1315291</t>
+          <t>1312505</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>53,39%</t>
         </is>
       </c>
     </row>
